--- a/data/processed/adidas_sentiment.xlsx
+++ b/data/processed/adidas_sentiment.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context_human</t>
+          <t>Leadership_context</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence_human</t>
+          <t>Information_valence</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/data/processed/adidas_sentiment.xlsx
+++ b/data/processed/adidas_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z220"/>
+  <dimension ref="A1:AB220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>finbert_n_chunks</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>financial_roberta_score</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>finbert_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +659,12 @@
       <c r="Z2" t="n">
         <v>1</v>
       </c>
+      <c r="AA2" t="n">
+        <v>0.9974368897965178</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6905991276726127</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +767,12 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
+      <c r="AA3" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +875,12 @@
       <c r="Z4" t="n">
         <v>1</v>
       </c>
+      <c r="AA4" t="n">
+        <v>0.9975936454720795</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7638278175145388</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -955,6 +983,12 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>-0.9988018436124548</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.8997508818283677</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1057,6 +1091,12 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
+      <c r="AA6" t="n">
+        <v>-0.9979124876263086</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.8516850359737873</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1158,6 +1198,12 @@
       </c>
       <c r="Z7" t="n">
         <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9974581756978296</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02747631818056107</v>
       </c>
     </row>
     <row r="8">
@@ -1264,6 +1310,12 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>0.9974743600469083</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.5315780378878117</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1366,6 +1418,12 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>0.997445733693894</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8688894864171743</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1468,6 +1526,12 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" t="n">
+        <v>0.002424683945719153</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.0927644744515419</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1570,6 +1634,12 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
+      <c r="AA11" t="n">
+        <v>0.9972773440531455</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9237083466723561</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1672,6 +1742,12 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>-0.9985550028213765</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.9647365249693394</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1774,6 +1850,12 @@
       <c r="Z13" t="n">
         <v>1</v>
       </c>
+      <c r="AA13" t="n">
+        <v>0.9974178409320302</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7691473178565502</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1876,6 +1958,12 @@
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="n">
+        <v>0.9973013259004802</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9352905759587884</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1978,6 +2066,12 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AA15" t="n">
+        <v>0.9768972752208356</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.03292051330208778</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2080,6 +2174,12 @@
       <c r="Z16" t="n">
         <v>1</v>
       </c>
+      <c r="AA16" t="n">
+        <v>0.9974397728801705</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.4391233585774899</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2182,6 +2282,12 @@
       <c r="Z17" t="n">
         <v>1</v>
       </c>
+      <c r="AA17" t="n">
+        <v>0.997457179473713</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.5717343213036656</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2284,6 +2390,12 @@
       <c r="Z18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>0.9971380465431139</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.4192639756947756</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2386,6 +2498,12 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
+      <c r="AA19" t="n">
+        <v>0.9971913469489664</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.5051892651244998</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2488,6 +2606,12 @@
       <c r="Z20" t="n">
         <v>1</v>
       </c>
+      <c r="AA20" t="n">
+        <v>0.9971543662250042</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.3439348936080933</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2589,6 +2713,12 @@
       </c>
       <c r="Z21" t="n">
         <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.9971717020380311</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.7580521712079644</v>
       </c>
     </row>
     <row r="22">
@@ -2697,6 +2827,12 @@
       <c r="Z22" t="n">
         <v>1</v>
       </c>
+      <c r="AA22" t="n">
+        <v>0.8369296416640282</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.2332699485123158</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2799,6 +2935,12 @@
       <c r="Z23" t="n">
         <v>1</v>
       </c>
+      <c r="AA23" t="n">
+        <v>0.9976327135227621</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.6071839705109596</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2901,6 +3043,12 @@
       <c r="Z24" t="n">
         <v>1</v>
       </c>
+      <c r="AA24" t="n">
+        <v>0.9976155620533973</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.9294916186481714</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3003,6 +3151,12 @@
       <c r="Z25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>0.9962211812089663</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.7554853856563568</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3105,6 +3259,12 @@
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AA26" t="n">
+        <v>0.9974225451005623</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.9132846128195524</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3207,6 +3367,12 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="n">
+        <v>0.0009704874537419528</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.001205779612064362</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3309,6 +3475,12 @@
       <c r="Z28" t="n">
         <v>1</v>
       </c>
+      <c r="AA28" t="n">
+        <v>0.9975313473842107</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.9306424548849463</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3411,6 +3583,12 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>-0.0001785313943400979</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.1384926941245794</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3513,6 +3691,12 @@
       <c r="Z30" t="n">
         <v>1</v>
       </c>
+      <c r="AA30" t="n">
+        <v>0.9935892853391124</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.8717485554516315</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3617,6 +3801,12 @@
       <c r="Z31" t="n">
         <v>1</v>
       </c>
+      <c r="AA31" t="n">
+        <v>0.0002153951209038496</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.05680410377681255</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3719,6 +3909,12 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>0.06198042185860686</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.7025059629231691</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3821,6 +4017,12 @@
       <c r="Z33" t="n">
         <v>1</v>
       </c>
+      <c r="AA33" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3923,6 +4125,12 @@
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>0.9969654694432393</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.9401136226952076</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4025,6 +4233,12 @@
       <c r="Z35" t="n">
         <v>1</v>
       </c>
+      <c r="AA35" t="n">
+        <v>0.0003283769183326513</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.1669206880033016</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4127,6 +4341,12 @@
       <c r="Z36" t="n">
         <v>1</v>
       </c>
+      <c r="AA36" t="n">
+        <v>0.9954709385638125</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.141121132299304</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4229,6 +4449,12 @@
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>0.03900580480694771</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.05810968950390816</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4331,6 +4557,12 @@
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AA38" t="n">
+        <v>0.9973830805392936</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.3047980535775423</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4433,6 +4665,12 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>0.9973345051403157</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9194993376731873</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4535,6 +4773,12 @@
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AA40" t="n">
+        <v>0.9929046153556556</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-0.7012293040752411</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4637,6 +4881,12 @@
       <c r="Z41" t="n">
         <v>1</v>
       </c>
+      <c r="AA41" t="n">
+        <v>0.9971370578277856</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.9410649780184031</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4739,6 +4989,12 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" t="n">
+        <v>0.9962891463655978</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.1022175503894687</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4841,6 +5097,12 @@
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AA43" t="n">
+        <v>0.9976235001231544</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.8989890431985259</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4943,6 +5205,12 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>0.007859148274292238</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.02456275932490826</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5045,6 +5313,12 @@
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>0.9976231430773623</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.5661713881418109</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5147,6 +5421,12 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>0.8819078207015991</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.1888994220644236</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5250,6 +5530,12 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="n">
+        <v>0.9975709795253351</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.790991498157382</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5352,6 +5638,12 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="n">
+        <v>0.9977125299046747</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.12681520357728</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5454,6 +5746,12 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>0.9974113672506064</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.9223013482987881</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5556,6 +5854,12 @@
       <c r="Z50" t="n">
         <v>1</v>
       </c>
+      <c r="AA50" t="n">
+        <v>0.0007375395143753849</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.392067083157599</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5658,6 +5962,12 @@
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>0.9459259333088994</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.05877911858260632</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5760,6 +6070,12 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>0.99749271949986</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.5397892938926816</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5862,6 +6178,12 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>0.9974468111176975</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.9100999888032675</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5964,6 +6286,12 @@
       <c r="Z54" t="n">
         <v>1</v>
       </c>
+      <c r="AA54" t="n">
+        <v>0.9975726574775763</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.8263978487811983</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6066,6 +6394,12 @@
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>0.9973704216536134</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.5442973393946886</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6168,6 +6502,12 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
+      <c r="AA56" t="n">
+        <v>0.9974094302742742</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.9382840674370527</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6269,6 +6609,12 @@
       </c>
       <c r="Z57" t="n">
         <v>1</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.006065401248633862</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.04676091391593218</v>
       </c>
     </row>
     <row r="58">
@@ -6375,6 +6721,12 @@
       <c r="Z58" t="n">
         <v>1</v>
       </c>
+      <c r="AA58" t="n">
+        <v>0.9968837756314315</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.4393031345680356</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6477,6 +6829,12 @@
       <c r="Z59" t="n">
         <v>1</v>
       </c>
+      <c r="AA59" t="n">
+        <v>0.9972808917518705</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.1504397233948112</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6579,6 +6937,12 @@
       <c r="Z60" t="n">
         <v>1</v>
       </c>
+      <c r="AA60" t="n">
+        <v>0.0002909393515437841</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.04001524671912193</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6681,6 +7045,12 @@
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>0.2641189561400097</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.1211056746542454</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6783,6 +7153,12 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AA62" t="n">
+        <v>-4.622619599103928e-06</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.01981780305504799</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6885,6 +7261,12 @@
       <c r="Z63" t="n">
         <v>1</v>
       </c>
+      <c r="AA63" t="n">
+        <v>0.9244178085646126</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.7994051799178123</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6987,6 +7369,12 @@
       <c r="Z64" t="n">
         <v>1</v>
       </c>
+      <c r="AA64" t="n">
+        <v>4.041986539959908e-05</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.02518966980278492</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7089,6 +7477,12 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>-0.003557731193723157</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.1152844093739986</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7191,6 +7585,12 @@
       <c r="Z66" t="n">
         <v>1</v>
       </c>
+      <c r="AA66" t="n">
+        <v>3.192952135577798e-05</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.01038388162851334</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7293,6 +7693,12 @@
       <c r="Z67" t="n">
         <v>1</v>
       </c>
+      <c r="AA67" t="n">
+        <v>0.0001207893947139382</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.08941008895635605</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7395,6 +7801,12 @@
       <c r="Z68" t="n">
         <v>1</v>
       </c>
+      <c r="AA68" t="n">
+        <v>0.1829243593092542</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.07435361854732037</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7497,6 +7909,12 @@
       <c r="Z69" t="n">
         <v>1</v>
       </c>
+      <c r="AA69" t="n">
+        <v>0.0003970547404605895</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.05410967953503132</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7599,6 +8017,12 @@
       <c r="Z70" t="n">
         <v>1</v>
       </c>
+      <c r="AA70" t="n">
+        <v>0.0001168692979263142</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.02549014240503311</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7701,6 +8125,12 @@
       <c r="Z71" t="n">
         <v>1</v>
       </c>
+      <c r="AA71" t="n">
+        <v>-5.808730202261358e-05</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.05914942175149918</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7803,6 +8233,12 @@
       <c r="Z72" t="n">
         <v>1</v>
       </c>
+      <c r="AA72" t="n">
+        <v>0.004802173265488818</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.09647095948457718</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7905,6 +8341,12 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
+      <c r="AA73" t="n">
+        <v>0.0002124157617799938</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.0001721791923046112</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8007,6 +8449,12 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
+      <c r="AA74" t="n">
+        <v>-0.5517434310168028</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.3361619785428047</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8109,6 +8557,12 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
+      <c r="AA75" t="n">
+        <v>-0.9983229696226772</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04939316213130951</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8211,6 +8665,12 @@
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>0.000845909264171496</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.2977480599656701</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8313,6 +8773,12 @@
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AA77" t="n">
+        <v>-0.998688725172542</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>-0.9527278812602162</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8415,6 +8881,12 @@
       <c r="Z78" t="n">
         <v>1</v>
       </c>
+      <c r="AA78" t="n">
+        <v>0.9975749871809967</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.7676642695441842</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8517,6 +8989,12 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
+      <c r="AA79" t="n">
+        <v>0.9320178421330638</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.1888089012354612</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8619,6 +9097,12 @@
       <c r="Z80" t="n">
         <v>1</v>
       </c>
+      <c r="AA80" t="n">
+        <v>4.277238622307777e-05</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.05494553782045841</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8721,6 +9205,12 @@
       <c r="Z81" t="n">
         <v>1</v>
       </c>
+      <c r="AA81" t="n">
+        <v>-3.550245310179889e-06</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.1437055189162493</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8823,6 +9313,12 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
+      <c r="AA82" t="n">
+        <v>0.003364685748238117</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.2411477323621511</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8925,6 +9421,12 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="n">
+        <v>-0.00026610994245857</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.03572715632617474</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9027,6 +9529,12 @@
       <c r="Z84" t="n">
         <v>1</v>
       </c>
+      <c r="AA84" t="n">
+        <v>-0.9951257876527961</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>-0.1854532659053802</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9129,6 +9637,12 @@
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AA85" t="n">
+        <v>0.0001574460766278207</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.04891327954828739</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9231,6 +9745,12 @@
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AA86" t="n">
+        <v>0.001780817357939668</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.233240008354187</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9333,6 +9853,12 @@
       <c r="Z87" t="n">
         <v>1</v>
       </c>
+      <c r="AA87" t="n">
+        <v>-4.676112439483404e-05</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.004435546696186066</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9435,6 +9961,12 @@
       <c r="Z88" t="n">
         <v>1</v>
       </c>
+      <c r="AA88" t="n">
+        <v>0.002852620207704604</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.07911061495542526</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9537,6 +10069,12 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="n">
+        <v>0.993371449469123</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.8045403324067593</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9639,6 +10177,12 @@
       <c r="Z90" t="n">
         <v>1</v>
       </c>
+      <c r="AA90" t="n">
+        <v>2.962668077088892e-05</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.04422866925597191</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9741,6 +10285,12 @@
       <c r="Z91" t="n">
         <v>1</v>
       </c>
+      <c r="AA91" t="n">
+        <v>0.9960451357619604</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.7442705929279327</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9843,6 +10393,12 @@
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AA92" t="n">
+        <v>0.000142287986818701</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.01263921894133091</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9945,6 +10501,12 @@
       <c r="Z93" t="n">
         <v>1</v>
       </c>
+      <c r="AA93" t="n">
+        <v>0.9975921264267527</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.2829457111656666</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10047,6 +10609,12 @@
       <c r="Z94" t="n">
         <v>1</v>
       </c>
+      <c r="AA94" t="n">
+        <v>0.9960426338948309</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>-0.02607222646474838</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10157,6 +10725,12 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
+      <c r="AA95" t="n">
+        <v>0.9975240502390079</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.08457564376294613</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10259,6 +10833,12 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
+      <c r="AA96" t="n">
+        <v>0.9919342739012791</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.0417476873844862</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10361,6 +10941,12 @@
       <c r="Z97" t="n">
         <v>1</v>
       </c>
+      <c r="AA97" t="n">
+        <v>0.9944969187054085</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.1151821985840797</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10463,6 +11049,12 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
+      <c r="AA98" t="n">
+        <v>0.9950844158011023</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.06228513270616531</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10569,6 +11161,12 @@
       <c r="Z99" t="n">
         <v>1</v>
       </c>
+      <c r="AA99" t="n">
+        <v>0.001452153694117442</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.02049102261662483</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10671,6 +11269,12 @@
       <c r="Z100" t="n">
         <v>1</v>
       </c>
+      <c r="AA100" t="n">
+        <v>0.997211304231314</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.8138167383149266</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10773,6 +11377,12 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>0.0001409281685482711</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.02353473380208015</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10875,6 +11485,12 @@
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>0.9966945697087795</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.1760267950594425</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10977,6 +11593,12 @@
       <c r="Z103" t="n">
         <v>1</v>
       </c>
+      <c r="AA103" t="n">
+        <v>0.9967597359791398</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.6627229806035757</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11080,6 +11702,12 @@
       <c r="Z104" t="n">
         <v>1</v>
       </c>
+      <c r="AA104" t="n">
+        <v>0.0002175019471906126</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.02286222949624062</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11182,6 +11810,12 @@
       <c r="Z105" t="n">
         <v>1</v>
       </c>
+      <c r="AA105" t="n">
+        <v>0.9971476705395617</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.8836501613259315</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11292,6 +11926,12 @@
       <c r="Z106" t="n">
         <v>1</v>
       </c>
+      <c r="AA106" t="n">
+        <v>0.9972291710437275</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.4709140956401825</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11394,6 +12034,12 @@
       <c r="Z107" t="n">
         <v>1</v>
       </c>
+      <c r="AA107" t="n">
+        <v>0.997466683445964</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0.1759531013667583</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11496,6 +12142,12 @@
       <c r="Z108" t="n">
         <v>1</v>
       </c>
+      <c r="AA108" t="n">
+        <v>0.9937457123305649</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0.5918761715292931</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11598,6 +12250,12 @@
       <c r="Z109" t="n">
         <v>1</v>
       </c>
+      <c r="AA109" t="n">
+        <v>0.9974042081157677</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0.8475246233865619</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11708,6 +12366,12 @@
       <c r="Z110" t="n">
         <v>1</v>
       </c>
+      <c r="AA110" t="n">
+        <v>0.0817656205908861</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.1188738970085979</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11810,6 +12474,12 @@
       <c r="Z111" t="n">
         <v>1</v>
       </c>
+      <c r="AA111" t="n">
+        <v>0.9957420432037907</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.1309853391721845</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11912,6 +12582,12 @@
       <c r="Z112" t="n">
         <v>1</v>
       </c>
+      <c r="AA112" t="n">
+        <v>-6.15464523434639e-06</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0.02166026271879673</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12014,6 +12690,12 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AA113" t="n">
+        <v>0.9976107379770838</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.2947686202824116</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12116,6 +12798,12 @@
       <c r="Z114" t="n">
         <v>1</v>
       </c>
+      <c r="AA114" t="n">
+        <v>0.9976174730109051</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.2984937578439713</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12218,6 +12906,12 @@
       <c r="Z115" t="n">
         <v>1</v>
       </c>
+      <c r="AA115" t="n">
+        <v>0.997333308274392</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0.8420784389600158</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12320,6 +13014,12 @@
       <c r="Z116" t="n">
         <v>1</v>
       </c>
+      <c r="AA116" t="n">
+        <v>2.256454899907112e-05</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0.000476498156785965</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12422,6 +13122,12 @@
       <c r="Z117" t="n">
         <v>1</v>
       </c>
+      <c r="AA117" t="n">
+        <v>0.9959813611931168</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.5178651893511415</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12524,6 +13230,12 @@
       <c r="Z118" t="n">
         <v>1</v>
       </c>
+      <c r="AA118" t="n">
+        <v>0.9975466973846778</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.1274071373045444</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12626,6 +13338,12 @@
       <c r="Z119" t="n">
         <v>1</v>
       </c>
+      <c r="AA119" t="n">
+        <v>0.9891533362533664</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.2097847480326891</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12728,6 +13446,12 @@
       <c r="Z120" t="n">
         <v>1</v>
       </c>
+      <c r="AA120" t="n">
+        <v>0.9635529321967624</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.02699730545282364</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12838,6 +13562,12 @@
       <c r="Z121" t="n">
         <v>1</v>
       </c>
+      <c r="AA121" t="n">
+        <v>0.9971130330814049</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.2351294606924057</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12948,6 +13678,12 @@
       <c r="Z122" t="n">
         <v>1</v>
       </c>
+      <c r="AA122" t="n">
+        <v>0.0001870022679213434</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.02223959192633629</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13050,6 +13786,12 @@
       <c r="Z123" t="n">
         <v>1</v>
       </c>
+      <c r="AA123" t="n">
+        <v>0.7517993673973251</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.1470455639064312</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13156,6 +13898,12 @@
       <c r="Z124" t="n">
         <v>1</v>
       </c>
+      <c r="AA124" t="n">
+        <v>0.9937063527759165</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.2297210851684213</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13258,6 +14006,12 @@
       <c r="Z125" t="n">
         <v>1</v>
       </c>
+      <c r="AA125" t="n">
+        <v>0.001588756626006216</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.01832378655672073</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13360,6 +14114,12 @@
       <c r="Z126" t="n">
         <v>1</v>
       </c>
+      <c r="AA126" t="n">
+        <v>0.0005351559375412762</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.01318785734474659</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13462,6 +14222,12 @@
       <c r="Z127" t="n">
         <v>1</v>
       </c>
+      <c r="AA127" t="n">
+        <v>0.002443589430185966</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.02485514432191849</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13564,6 +14330,12 @@
       <c r="Z128" t="n">
         <v>1</v>
       </c>
+      <c r="AA128" t="n">
+        <v>0.9008098497142782</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.028552221134305</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13666,6 +14438,12 @@
       <c r="Z129" t="n">
         <v>1</v>
       </c>
+      <c r="AA129" t="n">
+        <v>0.3725673985027242</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.1177819035947323</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13768,6 +14546,12 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
+      <c r="AA130" t="n">
+        <v>0.792423386592418</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.05613825656473637</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13870,6 +14654,12 @@
       <c r="Z131" t="n">
         <v>1</v>
       </c>
+      <c r="AA131" t="n">
+        <v>0.9971827437402681</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.607153695076704</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13972,6 +14762,12 @@
       <c r="Z132" t="n">
         <v>1</v>
       </c>
+      <c r="AA132" t="n">
+        <v>-0.9961534323665546</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>-0.2138819806277752</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14074,6 +14870,12 @@
       <c r="Z133" t="n">
         <v>1</v>
       </c>
+      <c r="AA133" t="n">
+        <v>0.06505036354064941</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.8140643425285816</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14176,6 +14978,12 @@
       <c r="Z134" t="n">
         <v>1</v>
       </c>
+      <c r="AA134" t="n">
+        <v>0.0001090466976165771</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.04660630039870739</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14278,6 +15086,12 @@
       <c r="Z135" t="n">
         <v>1</v>
       </c>
+      <c r="AA135" t="n">
+        <v>0.9955512852175161</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.007962688803672791</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14380,6 +15194,12 @@
       <c r="Z136" t="n">
         <v>1</v>
       </c>
+      <c r="AA136" t="n">
+        <v>0.9975366790313274</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.2374185668304563</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14482,6 +15302,12 @@
       <c r="Z137" t="n">
         <v>1</v>
       </c>
+      <c r="AA137" t="n">
+        <v>0.9974226832273416</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3915773583576083</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14584,6 +15410,12 @@
       <c r="Z138" t="n">
         <v>1</v>
       </c>
+      <c r="AA138" t="n">
+        <v>0.9976345960167237</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.7961348062381148</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14686,6 +15518,12 @@
       <c r="Z139" t="n">
         <v>1</v>
       </c>
+      <c r="AA139" t="n">
+        <v>0.0002288614923600107</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.003106089308857918</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14788,6 +15626,12 @@
       <c r="Z140" t="n">
         <v>1</v>
       </c>
+      <c r="AA140" t="n">
+        <v>0.005469558906042948</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.1322694849222898</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14890,6 +15734,12 @@
       <c r="Z141" t="n">
         <v>1</v>
       </c>
+      <c r="AA141" t="n">
+        <v>0.001488764799432829</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.02552881650626659</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14992,6 +15842,12 @@
       <c r="Z142" t="n">
         <v>1</v>
       </c>
+      <c r="AA142" t="n">
+        <v>0.8724369177944027</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.0163038931787014</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15094,6 +15950,12 @@
       <c r="Z143" t="n">
         <v>1</v>
       </c>
+      <c r="AA143" t="n">
+        <v>0.9976065783994272</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.8543398100882769</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15196,6 +16058,12 @@
       <c r="Z144" t="n">
         <v>1</v>
       </c>
+      <c r="AA144" t="n">
+        <v>0.9972187085077167</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>-0.01991734653711319</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15298,6 +16166,12 @@
       <c r="Z145" t="n">
         <v>1</v>
       </c>
+      <c r="AA145" t="n">
+        <v>0.997623065370135</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0.4453241974115372</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15400,6 +16274,12 @@
       <c r="Z146" t="n">
         <v>1</v>
       </c>
+      <c r="AA146" t="n">
+        <v>0.00012891624646727</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>-0.03496655076742172</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15503,6 +16383,12 @@
       <c r="Z147" t="n">
         <v>1</v>
       </c>
+      <c r="AA147" t="n">
+        <v>0.9972169579123147</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0.1831861436367035</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15605,6 +16491,12 @@
       <c r="Z148" t="n">
         <v>1</v>
       </c>
+      <c r="AA148" t="n">
+        <v>0.9972975545097142</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0.1164743304252625</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15707,6 +16599,12 @@
       <c r="Z149" t="n">
         <v>1</v>
       </c>
+      <c r="AA149" t="n">
+        <v>0.9972447723848745</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0.1593888653442264</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15813,6 +16711,12 @@
       <c r="Z150" t="n">
         <v>1</v>
       </c>
+      <c r="AA150" t="n">
+        <v>0.9971740431210492</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0.05421654880046844</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15915,6 +16819,12 @@
       <c r="Z151" t="n">
         <v>1</v>
       </c>
+      <c r="AA151" t="n">
+        <v>0.9971068168524653</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0.333432606421411</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16017,6 +16927,12 @@
       <c r="Z152" t="n">
         <v>1</v>
       </c>
+      <c r="AA152" t="n">
+        <v>0.9955237208632752</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0.3768733069300652</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16119,6 +17035,12 @@
       <c r="Z153" t="n">
         <v>1</v>
       </c>
+      <c r="AA153" t="n">
+        <v>0.9673058985936223</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0.2584606613963842</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16221,6 +17143,12 @@
       <c r="Z154" t="n">
         <v>1</v>
       </c>
+      <c r="AA154" t="n">
+        <v>0.000177781272213906</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0.01696189492940903</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16323,6 +17251,12 @@
       <c r="Z155" t="n">
         <v>1</v>
       </c>
+      <c r="AA155" t="n">
+        <v>0.003702492409502156</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0.1271773725748062</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16425,6 +17359,12 @@
       <c r="Z156" t="n">
         <v>1</v>
       </c>
+      <c r="AA156" t="n">
+        <v>0.9766006860299967</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0.1792431813664734</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16528,6 +17468,12 @@
       <c r="Z157" t="n">
         <v>1</v>
       </c>
+      <c r="AA157" t="n">
+        <v>0.997584305878263</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0.05990302376449108</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16630,6 +17576,12 @@
       <c r="Z158" t="n">
         <v>1</v>
       </c>
+      <c r="AA158" t="n">
+        <v>0.001128784511820413</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0.1712782336398959</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16732,6 +17684,12 @@
       <c r="Z159" t="n">
         <v>1</v>
       </c>
+      <c r="AA159" t="n">
+        <v>0.0004382967890705913</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0.02923587337136269</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16834,6 +17792,12 @@
       <c r="Z160" t="n">
         <v>1</v>
       </c>
+      <c r="AA160" t="n">
+        <v>0.9605705371650402</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0.2233119290322065</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16937,6 +17901,12 @@
       <c r="Z161" t="n">
         <v>1</v>
       </c>
+      <c r="AA161" t="n">
+        <v>0.0003104333882220089</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0.02411044761538506</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -17040,6 +18010,12 @@
       <c r="Z162" t="n">
         <v>1</v>
       </c>
+      <c r="AA162" t="n">
+        <v>0.9901328871783335</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0.1300372928380966</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17142,6 +18118,12 @@
       <c r="Z163" t="n">
         <v>1</v>
       </c>
+      <c r="AA163" t="n">
+        <v>0.002782298077363521</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0.03117424435913563</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17244,6 +18226,12 @@
       <c r="Z164" t="n">
         <v>1</v>
       </c>
+      <c r="AA164" t="n">
+        <v>0.9964436047594063</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0.5643325820565224</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17346,6 +18334,12 @@
       <c r="Z165" t="n">
         <v>1</v>
       </c>
+      <c r="AA165" t="n">
+        <v>-0.0001843132777139544</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>-0.01991726830601692</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17448,6 +18442,12 @@
       <c r="Z166" t="n">
         <v>1</v>
       </c>
+      <c r="AA166" t="n">
+        <v>0.03538164423662238</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>-0.2682451978325844</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17550,6 +18550,12 @@
       <c r="Z167" t="n">
         <v>1</v>
       </c>
+      <c r="AA167" t="n">
+        <v>0.0004942907398799434</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0.05155988968908787</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17652,6 +18658,12 @@
       <c r="Z168" t="n">
         <v>1</v>
       </c>
+      <c r="AA168" t="n">
+        <v>0.9971674025000539</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0.3318375684320927</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17754,6 +18766,12 @@
       <c r="Z169" t="n">
         <v>1</v>
       </c>
+      <c r="AA169" t="n">
+        <v>0.9974538993556052</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0.7849387032911181</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17856,6 +18874,12 @@
       <c r="Z170" t="n">
         <v>1</v>
       </c>
+      <c r="AA170" t="n">
+        <v>0.9975141396862455</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0.4987674113363028</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17959,6 +18983,12 @@
       <c r="Z171" t="n">
         <v>1</v>
       </c>
+      <c r="AA171" t="n">
+        <v>0.5147052407264709</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>0.5786570366472006</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18061,6 +19091,12 @@
       <c r="Z172" t="n">
         <v>1</v>
       </c>
+      <c r="AA172" t="n">
+        <v>0.9968397926131729</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>0.08304729498922825</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -18163,6 +19199,12 @@
       <c r="Z173" t="n">
         <v>1</v>
       </c>
+      <c r="AA173" t="n">
+        <v>-0.009289515670388937</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>0.6736506521701813</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -18265,6 +19307,12 @@
       <c r="Z174" t="n">
         <v>1</v>
       </c>
+      <c r="AA174" t="n">
+        <v>0.1068731176201254</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>0.1674488931894302</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18367,6 +19415,12 @@
       <c r="Z175" t="n">
         <v>1</v>
       </c>
+      <c r="AA175" t="n">
+        <v>0.4340635638218373</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>0.2733697313815355</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18469,6 +19523,12 @@
       <c r="Z176" t="n">
         <v>1</v>
       </c>
+      <c r="AA176" t="n">
+        <v>0.9916848339053104</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>-0.08585142157971859</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18571,6 +19631,12 @@
       <c r="Z177" t="n">
         <v>1</v>
       </c>
+      <c r="AA177" t="n">
+        <v>0.001173514654510655</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>0.1784206768497825</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18673,6 +19739,12 @@
       <c r="Z178" t="n">
         <v>1</v>
       </c>
+      <c r="AA178" t="n">
+        <v>-0.3191152925719507</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>-0.07526093348860741</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18775,6 +19847,12 @@
       <c r="Z179" t="n">
         <v>1</v>
       </c>
+      <c r="AA179" t="n">
+        <v>0.1140541912027402</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>0.07371390238404274</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18877,6 +19955,12 @@
       <c r="Z180" t="n">
         <v>1</v>
       </c>
+      <c r="AA180" t="n">
+        <v>-0.0267595550394617</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>-0.151669267565012</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18979,6 +20063,12 @@
       <c r="Z181" t="n">
         <v>1</v>
       </c>
+      <c r="AA181" t="n">
+        <v>0.2679936700733379</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>-0.003735944628715515</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -19081,6 +20171,12 @@
       <c r="Z182" t="n">
         <v>1</v>
       </c>
+      <c r="AA182" t="n">
+        <v>0.009056446549948305</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0.03599001653492451</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -19183,6 +20279,12 @@
       <c r="Z183" t="n">
         <v>1</v>
       </c>
+      <c r="AA183" t="n">
+        <v>0.9910925696312916</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>0.6016066502779722</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -19289,6 +20391,12 @@
       <c r="Z184" t="n">
         <v>1</v>
       </c>
+      <c r="AA184" t="n">
+        <v>0.9655352317495272</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>0.4486302733421326</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19391,6 +20499,12 @@
       <c r="Z185" t="n">
         <v>1</v>
       </c>
+      <c r="AA185" t="n">
+        <v>0.0003150029806420207</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>0.06882099993526936</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19493,6 +20607,12 @@
       <c r="Z186" t="n">
         <v>1</v>
       </c>
+      <c r="AA186" t="n">
+        <v>0.9470294563216157</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>0.2659519407898188</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19595,6 +20715,12 @@
       <c r="Z187" t="n">
         <v>1</v>
       </c>
+      <c r="AA187" t="n">
+        <v>-2.170944935642183e-05</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>0.0002794340252876282</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19697,6 +20823,12 @@
       <c r="Z188" t="n">
         <v>1</v>
       </c>
+      <c r="AA188" t="n">
+        <v>0.9973978734924458</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0.7704584719613194</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19799,6 +20931,12 @@
       <c r="Z189" t="n">
         <v>1</v>
       </c>
+      <c r="AA189" t="n">
+        <v>0.9965501032420434</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>0.1005369517952204</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19901,6 +21039,12 @@
       <c r="Z190" t="n">
         <v>1</v>
       </c>
+      <c r="AA190" t="n">
+        <v>0.9963284397235839</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>0.5848811101168394</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20003,6 +21147,12 @@
       <c r="Z191" t="n">
         <v>1</v>
       </c>
+      <c r="AA191" t="n">
+        <v>-5.122997390571982e-05</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>0.1613533310592175</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -20105,6 +21255,12 @@
       <c r="Z192" t="n">
         <v>1</v>
       </c>
+      <c r="AA192" t="n">
+        <v>2.980238059535623e-05</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>0.03821930475533009</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -20207,6 +21363,12 @@
       <c r="Z193" t="n">
         <v>1</v>
       </c>
+      <c r="AA193" t="n">
+        <v>-9.341747500002384e-06</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>0.03452974557876587</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20309,6 +21471,12 @@
       <c r="Z194" t="n">
         <v>1</v>
       </c>
+      <c r="AA194" t="n">
+        <v>0.9968604828754906</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>0.1709269341081381</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20411,6 +21579,12 @@
       <c r="Z195" t="n">
         <v>1</v>
       </c>
+      <c r="AA195" t="n">
+        <v>0.9976321296417154</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>0.3075676523149014</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20513,6 +21687,12 @@
       <c r="Z196" t="n">
         <v>1</v>
       </c>
+      <c r="AA196" t="n">
+        <v>0.9684534609987168</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>0.1938895294442773</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20615,6 +21795,12 @@
       <c r="Z197" t="n">
         <v>1</v>
       </c>
+      <c r="AA197" t="n">
+        <v>0.8220786251040408</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>0.2561210040003061</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20717,6 +21903,12 @@
       <c r="Z198" t="n">
         <v>1</v>
       </c>
+      <c r="AA198" t="n">
+        <v>0.0002745958045125008</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>0.1450811931863427</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20819,6 +22011,12 @@
       <c r="Z199" t="n">
         <v>1</v>
       </c>
+      <c r="AA199" t="n">
+        <v>0.8282151789753698</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0.2201303523033857</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20921,6 +22119,12 @@
       <c r="Z200" t="n">
         <v>1</v>
       </c>
+      <c r="AA200" t="n">
+        <v>0.002361058417591266</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>0.02865724079310894</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21023,6 +22227,12 @@
       <c r="Z201" t="n">
         <v>1</v>
       </c>
+      <c r="AA201" t="n">
+        <v>0.9866725471365498</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0.6547967279329896</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -21125,6 +22335,12 @@
       <c r="Z202" t="n">
         <v>1</v>
       </c>
+      <c r="AA202" t="n">
+        <v>0.9971798869373742</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>0.0545953530818224</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -21227,6 +22443,12 @@
       <c r="Z203" t="n">
         <v>1</v>
       </c>
+      <c r="AA203" t="n">
+        <v>0.002604369030450471</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>0.07733560353517532</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -21329,6 +22551,12 @@
       <c r="Z204" t="n">
         <v>1</v>
       </c>
+      <c r="AA204" t="n">
+        <v>0.9946451628347859</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>0.01316621899604797</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21431,6 +22659,12 @@
       <c r="Z205" t="n">
         <v>1</v>
       </c>
+      <c r="AA205" t="n">
+        <v>0.9973574035684578</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0.6552093857899308</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21533,6 +22767,12 @@
       <c r="Z206" t="n">
         <v>1</v>
       </c>
+      <c r="AA206" t="n">
+        <v>0.4014037084998563</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0.03046166524291039</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21635,6 +22875,12 @@
       <c r="Z207" t="n">
         <v>1</v>
       </c>
+      <c r="AA207" t="n">
+        <v>0.3514932554098777</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>0.3961554253473878</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21737,6 +22983,12 @@
       <c r="Z208" t="n">
         <v>1</v>
       </c>
+      <c r="AA208" t="n">
+        <v>-2.107155160047114e-05</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>0.09057449176907539</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21839,6 +23091,12 @@
       <c r="Z209" t="n">
         <v>1</v>
       </c>
+      <c r="AA209" t="n">
+        <v>0.9962768319237512</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>0.6345297610387206</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21945,6 +23203,12 @@
       <c r="Z210" t="n">
         <v>1</v>
       </c>
+      <c r="AA210" t="n">
+        <v>0.1050831606262363</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0.007057309150695801</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -22047,6 +23311,12 @@
       <c r="Z211" t="n">
         <v>1</v>
       </c>
+      <c r="AA211" t="n">
+        <v>0.9974851174629293</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0.7566924104467034</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -22149,6 +23419,12 @@
       <c r="Z212" t="n">
         <v>1</v>
       </c>
+      <c r="AA212" t="n">
+        <v>0.06184840752393939</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0.1593763660639524</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -22251,6 +23527,12 @@
       <c r="Z213" t="n">
         <v>1</v>
       </c>
+      <c r="AA213" t="n">
+        <v>0.6094564662780613</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0.06161704380065203</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -22353,6 +23635,12 @@
       <c r="Z214" t="n">
         <v>1</v>
       </c>
+      <c r="AA214" t="n">
+        <v>0.9972427982429508</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0.5983290262520313</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22455,6 +23743,12 @@
       <c r="Z215" t="n">
         <v>1</v>
       </c>
+      <c r="AA215" t="n">
+        <v>0.0005126397154526785</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0.01463829725980759</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22557,6 +23851,12 @@
       <c r="Z216" t="n">
         <v>1</v>
       </c>
+      <c r="AA216" t="n">
+        <v>0.9955847530945903</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0.8196003148332238</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22659,6 +23959,12 @@
       <c r="Z217" t="n">
         <v>1</v>
       </c>
+      <c r="AA217" t="n">
+        <v>0.0003465062618488446</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>0.03394790552556515</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22761,6 +24067,12 @@
       <c r="Z218" t="n">
         <v>1</v>
       </c>
+      <c r="AA218" t="n">
+        <v>0.9964314406679478</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0.1557417577132583</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22863,6 +24175,12 @@
       <c r="Z219" t="n">
         <v>1</v>
       </c>
+      <c r="AA219" t="n">
+        <v>6.715534254908562e-05</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0.003003424033522606</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22964,6 +24282,12 @@
       </c>
       <c r="Z220" t="n">
         <v>1</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>0.9967598658695351</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>0.2035676017403603</v>
       </c>
     </row>
   </sheetData>
